--- a/output/pdf_financials_xlsx/NVI.xlsx
+++ b/output/pdf_financials_xlsx/NVI.xlsx
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.188964</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.037642</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -2559,16 +2559,16 @@
         <v>0.9105799999999999</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.943384</v>
+        <v>0.743384</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.460909</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.588516</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.577132</v>
       </c>
       <c r="J34" s="1" t="inlineStr">
         <is>
@@ -2721,16 +2721,16 @@
         <v>0.9149119999999999</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.943384</v>
+        <v>0.743384</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.000206</v>
+        <v>0.461115</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>5.8e-05</v>
+        <v>0.588574</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.577132</v>
       </c>
       <c r="J36" s="1" t="inlineStr">
         <is>
@@ -3693,16 +3693,16 @@
         <v>0.00208</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0</v>
+        <v>0.005749</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.77182</v>
+        <v>1.310911</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.82374</v>
+        <v>0.235224</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.639475</v>
+        <v>0.062343</v>
       </c>
       <c r="J48" s="1" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -67320,7 +67320,7 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E548" s="5" t="n">
